--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/observations-summary.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="27">
   <si>
     <t>Profile</t>
   </si>
@@ -45,6 +45,54 @@
   </si>
   <si>
     <t>Method</t>
+  </si>
+  <si>
+    <t>tddui-observation-cause-deces</t>
+  </si>
+  <si>
+    <t>TDDUI Observation Cause Deces</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>[non précisé]#CAUSEDECES</t>
+  </si>
+  <si>
+    <t>dateTime, Period, Timing, instant</t>
+  </si>
+  <si>
+    <t>Quantity, CodeableConcept, string, boolean, integer, Range, Ratio, SampledData, time, dateTime, Period</t>
+  </si>
+  <si>
+    <t>optional</t>
+  </si>
+  <si>
+    <t>tddui-observation-periode-scolaire</t>
+  </si>
+  <si>
+    <t>TDDUI Obervation Periode Scolaire</t>
+  </si>
+  <si>
+    <t>[non précisé]#PERIODESCOL</t>
+  </si>
+  <si>
+    <t>[non précisé]#niveauScolaireReel</t>
+  </si>
+  <si>
+    <t>[non précisé]#niveauScolaireSuivi</t>
+  </si>
+  <si>
+    <t>[non précisé]#typeEnseignementSpecialise</t>
+  </si>
+  <si>
+    <t>[non précisé]#diplome</t>
+  </si>
+  <si>
+    <t>[non précisé]#volumeScolarisation</t>
+  </si>
+  <si>
+    <t>Quantity</t>
   </si>
 </sst>
 </file>
@@ -178,7 +226,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -216,6 +264,251 @@
         <v>10</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K2" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="F3" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J3" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K3" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H4" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I4" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J4" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K4" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F5" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G5" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H5" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I5" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J5" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K5" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D6" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="F6" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G6" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H6" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I6" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J6" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K6" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D7" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="F7" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G7" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H7" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I7" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J7" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K7" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D8" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E8" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="F8" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G8" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H8" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="I8" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J8" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K8" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/observations-summary.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="31">
   <si>
     <t>Profile</t>
   </si>
@@ -66,6 +66,18 @@
   </si>
   <si>
     <t>optional</t>
+  </si>
+  <si>
+    <t>tddui-observation-mobilite</t>
+  </si>
+  <si>
+    <t>TDDUI Obervation Mobilite</t>
+  </si>
+  <si>
+    <t>[non précisé]#MOBILITE</t>
+  </si>
+  <si>
+    <t>CodeableConcept</t>
   </si>
   <si>
     <t>tddui-observation-periode-scolaire</t>
@@ -226,7 +238,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -322,7 +334,7 @@
         <v>15</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I3" t="s" s="2">
         <v>17</v>
@@ -336,10 +348,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s" s="2">
         <v>13</v>
@@ -348,13 +360,13 @@
         <v>13</v>
       </c>
       <c r="E4" t="s" s="2">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F4" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>16</v>
@@ -374,7 +386,7 @@
         <v>13</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s" s="2">
         <v>13</v>
@@ -383,7 +395,7 @@
         <v>13</v>
       </c>
       <c r="E5" t="s" s="2">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F5" t="s" s="2">
         <v>13</v>
@@ -409,7 +421,7 @@
         <v>13</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s" s="2">
         <v>13</v>
@@ -418,7 +430,7 @@
         <v>13</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F6" t="s" s="2">
         <v>13</v>
@@ -444,7 +456,7 @@
         <v>13</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s" s="2">
         <v>13</v>
@@ -453,7 +465,7 @@
         <v>13</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F7" t="s" s="2">
         <v>13</v>
@@ -479,7 +491,7 @@
         <v>13</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s" s="2">
         <v>13</v>
@@ -488,7 +500,7 @@
         <v>13</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F8" t="s" s="2">
         <v>13</v>
@@ -497,7 +509,7 @@
         <v>13</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="I8" t="s" s="2">
         <v>17</v>
@@ -506,6 +518,41 @@
         <v>13</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D9" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E9" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="F9" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G9" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H9" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="I9" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J9" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="K9" t="s" s="2">
         <v>13</v>
       </c>
     </row>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/observations-summary.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/observations-summary.xlsx
@@ -56,7 +56,7 @@
     <t/>
   </si>
   <si>
-    <t>[non précisé]#CAUSEDECES</t>
+    <t>TDDUI Observation Type#CAUSEDECES</t>
   </si>
   <si>
     <t>dateTime, Period, Timing, instant</t>
@@ -74,7 +74,7 @@
     <t>TDDUI Obervation Mobilite</t>
   </si>
   <si>
-    <t>[non précisé]#MOBILITE</t>
+    <t>TDDUI Observation Type#MOBILITE</t>
   </si>
   <si>
     <t>CodeableConcept</t>
@@ -86,22 +86,22 @@
     <t>TDDUI Obervation Periode Scolaire</t>
   </si>
   <si>
-    <t>[non précisé]#PERIODESCOL</t>
-  </si>
-  <si>
-    <t>[non précisé]#niveauScolaireReel</t>
-  </si>
-  <si>
-    <t>[non précisé]#niveauScolaireSuivi</t>
-  </si>
-  <si>
-    <t>[non précisé]#typeEnseignementSpecialise</t>
-  </si>
-  <si>
-    <t>[non précisé]#diplome</t>
-  </si>
-  <si>
-    <t>[non précisé]#volumeScolarisation</t>
+    <t>TDDUI Observation Type#PERIODESCOL</t>
+  </si>
+  <si>
+    <t>TDDUI Observation Periode Scolaire#niveauScolaireReel</t>
+  </si>
+  <si>
+    <t>TDDUI Observation Periode Scolaire#niveauScolaireSuivi</t>
+  </si>
+  <si>
+    <t>TDDUI Observation Periode Scolaire#typeEnseignementSpecialise</t>
+  </si>
+  <si>
+    <t>TDDUI Observation Periode Scolaire#diplome</t>
+  </si>
+  <si>
+    <t>TDDUI Observation Periode Scolaire#volumeScolarisation</t>
   </si>
   <si>
     <t>Quantity</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/observations-summary.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/observations-summary.xlsx
@@ -47,16 +47,16 @@
     <t>Method</t>
   </si>
   <si>
-    <t>tddui-observation-cause-deces</t>
-  </si>
-  <si>
-    <t>TDDUI Observation Cause Deces</t>
+    <t>tddui-observation-cause-mortalite</t>
+  </si>
+  <si>
+    <t>TDDUI Observation Cause Mortalite</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>TDDUI Observation Type#CAUSEDECES</t>
+    <t>LOINC#79378-6</t>
   </si>
   <si>
     <t>dateTime, Period, Timing, instant</t>
@@ -68,13 +68,13 @@
     <t>optional</t>
   </si>
   <si>
-    <t>tddui-observation-mobilite</t>
-  </si>
-  <si>
-    <t>TDDUI Obervation Mobilite</t>
-  </si>
-  <si>
-    <t>TDDUI Observation Type#MOBILITE</t>
+    <t>tddui-observation-mobilite-usager</t>
+  </si>
+  <si>
+    <t>TDDUI Obervation Mobilite Usager</t>
+  </si>
+  <si>
+    <t>LOINC#LP73551-1</t>
   </si>
   <si>
     <t>CodeableConcept</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/observations-summary.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="29">
   <si>
     <t>Profile</t>
   </si>
@@ -87,12 +87,6 @@
   </si>
   <si>
     <t>TDDUI Observation Type#PERIODESCOL</t>
-  </si>
-  <si>
-    <t>TDDUI Observation Periode Scolaire#niveauScolaireReel</t>
-  </si>
-  <si>
-    <t>TDDUI Observation Periode Scolaire#niveauScolaireSuivi</t>
   </si>
   <si>
     <t>TDDUI Observation Periode Scolaire#typeEnseignementSpecialise</t>
@@ -238,7 +232,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -474,7 +468,7 @@
         <v>13</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>17</v>
@@ -483,76 +477,6 @@
         <v>13</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="C8" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D8" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E8" t="s" s="2">
-        <v>28</v>
-      </c>
-      <c r="F8" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G8" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="H8" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I8" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="J8" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="K8" t="s" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="C9" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D9" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E9" t="s" s="2">
-        <v>29</v>
-      </c>
-      <c r="F9" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G9" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="H9" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="I9" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="J9" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="K9" t="s" s="2">
         <v>13</v>
       </c>
     </row>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/observations-summary.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/observations-summary.xlsx
@@ -433,7 +433,7 @@
         <v>13</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I6" t="s" s="2">
         <v>17</v>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/observations-summary.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/observations-summary.xlsx
@@ -71,7 +71,7 @@
     <t>tddui-observation-mobilite-usager</t>
   </si>
   <si>
-    <t>TDDUI Obervation Mobilite Usager</t>
+    <t>TDDUI Observation Mobilite Usager</t>
   </si>
   <si>
     <t>LOINC#LP73551-1</t>
@@ -83,7 +83,7 @@
     <t>tddui-observation-periode-scolaire</t>
   </si>
   <si>
-    <t>TDDUI Obervation Periode Scolaire</t>
+    <t>TDDUI Observation Periode Scolaire</t>
   </si>
   <si>
     <t>TDDUI Observation Type#PERIODESCOL</t>
@@ -398,7 +398,7 @@
         <v>13</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I5" t="s" s="2">
         <v>17</v>
